--- a/resultados/previsoes.xlsx
+++ b/resultados/previsoes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/asbonato/mpe-fgv-eesp/_dissertacao/codigo/final/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80004DF8-AB70-FE47-B35B-24E3AEF46C51}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1937170-6F06-294E-A306-230555BA7A23}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection lockStructure="1"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="-21140" windowWidth="38400" windowHeight="21140" xr2:uid="{12009390-DD55-404C-A2F5-C0B9E283DAE6}"/>
@@ -4189,7 +4189,7 @@
         <v>12848621496.509701</v>
       </c>
       <c r="F86" s="7">
-        <v>12697109863.152241</v>
+        <v>12426645163.41712</v>
       </c>
       <c r="G86" s="7">
         <v>12029577328.977039</v>
@@ -4224,7 +4224,7 @@
         <v>12060161599.598301</v>
       </c>
       <c r="F87" s="7">
-        <v>11972999006.25738</v>
+        <v>11693115393.850639</v>
       </c>
       <c r="G87" s="7">
         <v>12039883866.048309</v>
@@ -4259,7 +4259,7 @@
         <v>12182890573.42235</v>
       </c>
       <c r="F88" s="7">
-        <v>12202926313.460939</v>
+        <v>11934849499.945789</v>
       </c>
       <c r="G88" s="7">
         <v>12040526882.387421</v>
@@ -4294,7 +4294,7 @@
         <v>12765974495.55813</v>
       </c>
       <c r="F89" s="7">
-        <v>12687261869.710711</v>
+        <v>12437716131.441681</v>
       </c>
       <c r="G89" s="7">
         <v>12045879028.998619</v>
@@ -4329,7 +4329,7 @@
         <v>12598115613.32822</v>
       </c>
       <c r="F90" s="7">
-        <v>12649579414.258089</v>
+        <v>12218944811.809811</v>
       </c>
       <c r="G90" s="7">
         <v>12060684465.074039</v>
@@ -4364,7 +4364,7 @@
         <v>12511439641.44342</v>
       </c>
       <c r="F91" s="7">
-        <v>12732735247.326891</v>
+        <v>12348913021.364479</v>
       </c>
       <c r="G91" s="7">
         <v>12070787419.498301</v>
@@ -4399,7 +4399,7 @@
         <v>12704306528.87479</v>
       </c>
       <c r="F92" s="7">
-        <v>12814682831.65024</v>
+        <v>12436005105.471069</v>
       </c>
       <c r="G92" s="7">
         <v>12084931945.021179</v>
@@ -4434,7 +4434,7 @@
         <v>12808134345.45578</v>
       </c>
       <c r="F93" s="7">
-        <v>12974595130.318319</v>
+        <v>12786883292.39492</v>
       </c>
       <c r="G93" s="7">
         <v>12107242035.665541</v>
@@ -4469,7 +4469,7 @@
         <v>13180154106.62187</v>
       </c>
       <c r="F94" s="7">
-        <v>13413161034.978251</v>
+        <v>13081833940.72378</v>
       </c>
       <c r="G94" s="7">
         <v>12126262278.31369</v>
@@ -4504,7 +4504,7 @@
         <v>13494013861.61915</v>
       </c>
       <c r="F95" s="7">
-        <v>13676061213.352489</v>
+        <v>13350844172.418039</v>
       </c>
       <c r="G95" s="7">
         <v>12147884026.90707</v>
@@ -4539,7 +4539,7 @@
         <v>13502128132.057489</v>
       </c>
       <c r="F96" s="7">
-        <v>13599793091.09325</v>
+        <v>13450522363.599979</v>
       </c>
       <c r="G96" s="7">
         <v>12169915718.875669</v>
@@ -4574,7 +4574,7 @@
         <v>14245000057.488979</v>
       </c>
       <c r="F97" s="7">
-        <v>14552076274.80258</v>
+        <v>14206038500.591551</v>
       </c>
       <c r="G97" s="7">
         <v>12183316572.618179</v>
